--- a/public/templates/process-docs/钢筋隐蔽工程质量验收记录.xlsx
+++ b/public/templates/process-docs/钢筋隐蔽工程质量验收记录.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">编号：</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-SG-ZHHC-03-01-05-YB-001</t>
+    <t xml:space="preserve">{{文件编号}}</t>
   </si>
   <si>
     <t xml:space="preserve">工程名称</t>
@@ -126,13 +126,13 @@
     <t xml:space="preserve">施工单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目经理</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">专业工长</t>
@@ -141,13 +141,13 @@
     <t xml:space="preserve">分包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">河南誉华美建设工程有限公司</t>
+    <t xml:space="preserve">{{分包单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">胡彦芳</t>
+    <t xml:space="preserve">{{分包单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">席桂华</t>
